--- a/analysis/coding_worksheets/決策群組_#101.xlsx
+++ b/analysis/coding_worksheets/決策群組_#101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,145 +451,150 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt2</t>
         </is>
@@ -618,17 +623,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -705,6 +712,9 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,17 +741,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>我也選Nancy</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -818,6 +830,9 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>我選 Amy</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -931,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,17 +977,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1044,6 +1066,9 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,17 +1095,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>我覺得Nancy注重細節很加分~因為財務需要很細心</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1157,6 +1184,9 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,17 +1213,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>他除了在公司具有一定年資外，也有完成公司內部領導課程</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1270,6 +1302,9 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1296,17 +1331,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>amy有18年的工作经验</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1383,6 +1420,9 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1409,17 +1449,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>nancy在專業上的能力也很出色~ 雖然工作經驗不那麼長</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1496,6 +1538,9 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1522,17 +1567,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>雖然Amy也不錯但作為一位領導幹部，還是要能有鼓勵下屬的能力</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1609,6 +1656,9 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,17 +1685,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>amy熟知财务部各个工作内容</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1722,6 +1774,9 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1748,10 +1803,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>目前大家討論重點整理如下：
 - 多數成員支持 Nancy，認為她注重細節且財務專業能力佳。
@@ -1761,9 +1821,6 @@
 目前針對「國際視野」與「個人經歷」的面向尚未有明確資訊，是否有成員知道 Nancy 或 Amy 在國際工作經驗、跨文化溝通或獨特個人經歷方面的表現呢？另外，合作特質方面，大家有觀察到她們在團隊中的協作表現嗎？</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1840,6 +1897,9 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1866,17 +1926,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>nancy有國際視野~ 也曾在會計部擔任多項職務 各方面能力都不錯</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1953,6 +2015,9 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1979,17 +2044,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Nancy雖然取得會計師資格在很早期。且在組織政治有不錯的觀察力，可以知道他是一個懂得察言觀色的領導者。</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -2066,6 +2133,9 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2092,17 +2162,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>amy注重细节</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -2179,6 +2251,9 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2205,17 +2280,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>nancy也滿注重細節的~~他在國外也有實務經歷 感覺可以讓團隊有更好的成長</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -2292,6 +2369,9 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2318,17 +2398,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Amy是台灣知名四大會計分析師前身，但Nancy有美國證交分析師經驗，在國際視野能力上優秀一點</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2405,6 +2487,9 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2431,17 +2516,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>如果考虑国际发展，我认为amy更有经验和领导力</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2518,6 +2605,9 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2544,10 +2634,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>目前討論摘要如下：
 - Nancy 具備國際視野，曾於國外有實務經驗，並取得會計師資格，熟悉多項職務，且注重細節。
@@ -2557,9 +2652,6 @@
 針對「合作特質」及「鼓勵下屬」這類軟性能力，大家目前討論較少，有沒有成員能補充 Nancy 或 Amy 在團隊合作、協調溝通、激勵同事等方面的觀察呢？這部分對領導職務也很關鍵。</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2636,6 +2728,9 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2662,17 +2757,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>nancy很嚴謹 但對下屬都很公平</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -2749,6 +2846,9 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2775,17 +2875,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Amy雖然過去有擔任調解中很適合的媒合的對象。但Nancy在內部發表了許多的文章，可以知道說他蠻適合整合各項的想法跟能力</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -2862,6 +2964,9 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2888,17 +2993,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>nancy不记得表扬他人贡献，这不利于团队合作</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -2975,6 +3082,9 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3001,17 +3111,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>amy有開會遲到的習慣 身為領導者不太好 應該以身作則</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -3088,6 +3200,9 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3114,17 +3229,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>雖然Amy注重細節，但Nancy有完成內部提供的領導課程，代表他是有受到公司肯定跟認可的一個不錯候選人</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -3201,6 +3318,9 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3227,17 +3347,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>amy如果迟到确实不好</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -3314,6 +3436,9 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3340,10 +3465,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>目前討論內容整理如下：
 - Nancy 嚴謹且對下屬公平，曾完成公司內部領導課程，發表多篇內部文章，展現整合想法與能力。
@@ -3353,9 +3483,6 @@
 目前「個人經歷」方面是否還有更多細節，例如兩位在重大專案、危機處理或跨部門合作的具體表現？也歡迎大家補充她們在激勵團隊、建立正向文化等經驗，幫助小組更全面評估。</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -3432,6 +3559,9 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3458,17 +3588,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>我們是不是有共識了</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -3545,6 +3677,9 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3571,17 +3706,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>有共識</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
@@ -3658,6 +3795,9 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3684,17 +3824,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>我认为有，迟到这个缺陷太严重了</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3771,6 +3913,9 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3797,17 +3942,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>有共识</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -3884,6 +4031,9 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3910,17 +4060,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
@@ -3997,6 +4149,9 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4023,17 +4178,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -4110,6 +4267,9 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4136,17 +4296,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -4223,6 +4385,9 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4249,17 +4414,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -4336,6 +4503,9 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4362,17 +4532,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -4449,6 +4621,9 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4475,17 +4650,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
@@ -4562,6 +4739,9 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0</v>
       </c>
     </row>
